--- a/output/yearly_benthic_cover_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_29_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>46.11294037309634</v>
+        <v>45.18346592598928</v>
       </c>
       <c r="M2" t="n">
-        <v>98.57760516388333</v>
+        <v>99.89562454510477</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9808276547856</v>
+        <v>88.09958967456832</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89220119235199</v>
+        <v>45.95210266488046</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228639005117575</v>
+        <v>2.228898145836894</v>
       </c>
       <c r="E3" t="n">
-        <v>5.683025531359085</v>
+        <v>5.723712577408175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428796683725249</v>
+        <v>0.742966048612298</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96093479847536</v>
+        <v>33.98048840608374</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17246474513615</v>
+        <v>34.1764382361657</v>
       </c>
       <c r="I3" t="n">
-        <v>6.549885978996621</v>
+        <v>6.603548456634649</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642997927328281</v>
+        <v>4.643537803826862</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01917234521442</v>
+        <v>11.90041032543168</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85350947977444</v>
+        <v>48.91047129969792</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648830173408</v>
+        <v>106.7629842900101</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0998061132975</v>
+        <v>87.322277954222</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64416384780821</v>
+        <v>42.81591296546071</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186314220703756</v>
+        <v>2.192186149183816</v>
       </c>
       <c r="E4" t="n">
-        <v>6.486708039415188</v>
+        <v>6.548527959233774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444347051410911</v>
+        <v>0.7445300316264744</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31597200255527</v>
+        <v>33.42079859748296</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24399643649019</v>
+        <v>34.24838145481782</v>
       </c>
       <c r="I4" t="n">
-        <v>5.469663801860184</v>
+        <v>5.514541064211704</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65271690713182</v>
+        <v>4.653312697665465</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90019388670251</v>
+        <v>12.677722045778</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27370098829495</v>
+        <v>44.3229330871881</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81805872280566</v>
+        <v>99.81656809842681</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.86037720278233</v>
+        <v>86.3807766777357</v>
       </c>
       <c r="C5" t="n">
-        <v>42.25367558533629</v>
+        <v>42.73044994218125</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125539984184051</v>
+        <v>2.147040241061844</v>
       </c>
       <c r="E5" t="n">
-        <v>7.067415479928537</v>
+        <v>7.180936598196145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457543623740979</v>
+        <v>0.7458526751857869</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38986872646009</v>
+        <v>32.73253026616143</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30470066920851</v>
+        <v>34.30922305854619</v>
       </c>
       <c r="I5" t="n">
-        <v>4.566133215788926</v>
+        <v>4.603614618673141</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660964764838113</v>
+        <v>4.661579219911168</v>
       </c>
       <c r="K5" t="n">
-        <v>14.13962279721766</v>
+        <v>13.61922332226429</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45476651183883</v>
+        <v>43.49714503932637</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84806489439279</v>
+        <v>99.84681830377191</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.51436465615687</v>
+        <v>85.29538258383789</v>
       </c>
       <c r="C6" t="n">
-        <v>41.61675117518086</v>
+        <v>42.36035660596753</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059828793977674</v>
+        <v>2.094775277753918</v>
       </c>
       <c r="E6" t="n">
-        <v>7.484064294617997</v>
+        <v>7.646483479641973</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468752539787115</v>
+        <v>0.7469725657613755</v>
       </c>
       <c r="G6" t="n">
-        <v>31.38853408186106</v>
+        <v>31.93572894841323</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35626168302073</v>
+        <v>34.36073802502327</v>
       </c>
       <c r="I6" t="n">
-        <v>3.810830211333756</v>
+        <v>3.84210575123552</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667970337366947</v>
+        <v>4.668578536008597</v>
       </c>
       <c r="K6" t="n">
-        <v>15.48563534384315</v>
+        <v>14.70461741616213</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77077644720406</v>
+        <v>42.80714779401831</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87316296622805</v>
+        <v>99.87212181614797</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.88395016611318</v>
+        <v>84.05996451866346</v>
       </c>
       <c r="C7" t="n">
-        <v>40.57816990818814</v>
+        <v>41.72216800517882</v>
       </c>
       <c r="D7" t="n">
-        <v>1.980311174905955</v>
+        <v>2.035264537146945</v>
       </c>
       <c r="E7" t="n">
-        <v>7.725108337169837</v>
+        <v>7.963557713905673</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478303559642616</v>
+        <v>0.7479221511141672</v>
       </c>
       <c r="G7" t="n">
-        <v>30.17681129031716</v>
+        <v>31.02846271239893</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40019637435604</v>
+        <v>34.40441895125168</v>
       </c>
       <c r="I7" t="n">
-        <v>3.179752908623296</v>
+        <v>3.205825008382536</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673939724776636</v>
+        <v>4.674513444463544</v>
       </c>
       <c r="K7" t="n">
-        <v>17.11604983388681</v>
+        <v>15.94003548133652</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19992386316581</v>
+        <v>42.23107135372813</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89414360524076</v>
+        <v>99.89327484024346</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.75781240962429</v>
+        <v>89.09527247247495</v>
       </c>
       <c r="C8" t="n">
-        <v>42.89795251190946</v>
+        <v>44.07205847380722</v>
       </c>
       <c r="D8" t="n">
-        <v>1.984531717221772</v>
+        <v>2.039654285083474</v>
       </c>
       <c r="E8" t="n">
-        <v>9.568445725662327</v>
+        <v>9.835545065118287</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494241709678809</v>
+        <v>0.7495353024562231</v>
       </c>
       <c r="G8" t="n">
-        <v>30.68697724869</v>
+        <v>31.54238037238025</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47351186452254</v>
+        <v>34.47862391298625</v>
       </c>
       <c r="I8" t="n">
-        <v>5.611020614010519</v>
+        <v>5.764937894099072</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683901068549257</v>
+        <v>4.684595640351394</v>
       </c>
       <c r="K8" t="n">
-        <v>12.2421875903757</v>
+        <v>10.90472752752505</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67322364614767</v>
+        <v>44.83146297921763</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81336374843283</v>
+        <v>99.80824898054992</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.58465662707221</v>
+        <v>87.59291527972157</v>
       </c>
       <c r="C9" t="n">
-        <v>41.59553149860244</v>
+        <v>43.46544365090971</v>
       </c>
       <c r="D9" t="n">
-        <v>1.885866210760287</v>
+        <v>1.972683584879506</v>
       </c>
       <c r="E9" t="n">
-        <v>9.873458929132569</v>
+        <v>10.31475375598336</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507914677111731</v>
+        <v>0.7509081109158587</v>
       </c>
       <c r="G9" t="n">
-        <v>29.16130440318227</v>
+        <v>30.50670716291194</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53640751471397</v>
+        <v>34.54177310212949</v>
       </c>
       <c r="I9" t="n">
-        <v>4.684381428377089</v>
+        <v>4.81291386967729</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692446673194833</v>
+        <v>4.693175693224116</v>
       </c>
       <c r="K9" t="n">
-        <v>14.41534337292781</v>
+        <v>12.40708472027844</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83326344474722</v>
+        <v>43.96733446508687</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84413831627748</v>
+        <v>99.83986283627502</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.2901155872768</v>
+        <v>85.84366788823765</v>
       </c>
       <c r="C10" t="n">
-        <v>40.02748850270996</v>
+        <v>42.46426548288416</v>
       </c>
       <c r="D10" t="n">
-        <v>1.782905481168973</v>
+        <v>1.894999703168032</v>
       </c>
       <c r="E10" t="n">
-        <v>9.986034229664572</v>
+        <v>10.57806377012155</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519662425317055</v>
+        <v>0.7520793916819981</v>
       </c>
       <c r="G10" t="n">
-        <v>27.56921416896804</v>
+        <v>29.30535918758777</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59044715645846</v>
+        <v>34.5956520173719</v>
       </c>
       <c r="I10" t="n">
-        <v>3.909759292661891</v>
+        <v>4.017017620293917</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699789015823161</v>
+        <v>4.700496198012488</v>
       </c>
       <c r="K10" t="n">
-        <v>16.7098844127232</v>
+        <v>14.15633211176235</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13250537822304</v>
+        <v>43.24571035341802</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8698782936562</v>
+        <v>99.86630794806453</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.9427005262912</v>
+        <v>83.88843680217843</v>
       </c>
       <c r="C11" t="n">
-        <v>38.28572718532851</v>
+        <v>41.13319008042984</v>
       </c>
       <c r="D11" t="n">
-        <v>1.678767119186624</v>
+        <v>1.808719536053369</v>
       </c>
       <c r="E11" t="n">
-        <v>9.946508095455732</v>
+        <v>10.65510210595368</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529765446835814</v>
+        <v>0.75308109908181</v>
       </c>
       <c r="G11" t="n">
-        <v>25.95891410818496</v>
+        <v>27.97107333844845</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63692105544475</v>
+        <v>34.64173055776325</v>
       </c>
       <c r="I11" t="n">
-        <v>3.262510199063165</v>
+        <v>3.351973295616575</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706103404272385</v>
+        <v>4.706756869261311</v>
       </c>
       <c r="K11" t="n">
-        <v>19.0572994737088</v>
+        <v>16.11156319782156</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54836891616652</v>
+        <v>42.64366289896265</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89139557520383</v>
+        <v>99.88841617721405</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.52458845383511</v>
+        <v>81.84770410926124</v>
       </c>
       <c r="C12" t="n">
-        <v>36.37218021159136</v>
+        <v>39.61279523323353</v>
       </c>
       <c r="D12" t="n">
-        <v>1.572572591755926</v>
+        <v>1.719390184326566</v>
       </c>
       <c r="E12" t="n">
-        <v>9.770967329288867</v>
+        <v>10.59494815337181</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538465595333647</v>
+        <v>0.7539387837213849</v>
       </c>
       <c r="G12" t="n">
-        <v>24.31681939187408</v>
+        <v>26.58963315459414</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67694173853478</v>
+        <v>34.68118405118369</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721899845764553</v>
+        <v>2.796492383804985</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71154099708353</v>
+        <v>4.712117398258655</v>
       </c>
       <c r="K12" t="n">
-        <v>21.4754115461649</v>
+        <v>18.15229589073875</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06178295893644</v>
+        <v>42.14179850670504</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9093747166927</v>
+        <v>99.90688963067733</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.09446260926262</v>
+        <v>79.56161893090979</v>
       </c>
       <c r="C13" t="n">
-        <v>34.36212167312484</v>
+        <v>37.76022681763538</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46686489223736</v>
+        <v>1.619936568458219</v>
       </c>
       <c r="E13" t="n">
-        <v>9.492584465799714</v>
+        <v>10.37089247254009</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545963350892493</v>
+        <v>0.754675614647375</v>
       </c>
       <c r="G13" t="n">
-        <v>22.68225253562913</v>
+        <v>25.05162555984157</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71143141410547</v>
+        <v>34.71507827377923</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270505872093877</v>
+        <v>2.332687850097208</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716227094307809</v>
+        <v>4.716722591546093</v>
       </c>
       <c r="K13" t="n">
-        <v>23.90553739073738</v>
+        <v>20.43838106909019</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65673260708877</v>
+        <v>41.72371176927984</v>
       </c>
       <c r="M13" t="n">
-        <v>99.924391670951</v>
+        <v>99.92231965600541</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.32241361195167</v>
+        <v>85.40723340173609</v>
       </c>
       <c r="C14" t="n">
-        <v>38.71681873812889</v>
+        <v>41.24436225303067</v>
       </c>
       <c r="D14" t="n">
-        <v>1.468731307492361</v>
+        <v>1.62194055338316</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93271685386761</v>
+        <v>12.37360845240875</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555564713080866</v>
+        <v>0.755609205865958</v>
       </c>
       <c r="G14" t="n">
-        <v>24.6090767618243</v>
+        <v>26.54422645904226</v>
       </c>
       <c r="H14" t="n">
-        <v>36.65356137369348</v>
+        <v>36.21963360004742</v>
       </c>
       <c r="I14" t="n">
-        <v>3.180542898090289</v>
+        <v>3.169657594326316</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722227945675542</v>
+        <v>4.722557536662237</v>
       </c>
       <c r="K14" t="n">
-        <v>16.67758638804833</v>
+        <v>14.59276659826389</v>
       </c>
       <c r="L14" t="n">
-        <v>44.49971150151671</v>
+        <v>44.05734643766654</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89411662769393</v>
+        <v>99.8944752889611</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.60599304225458</v>
+        <v>84.79652742483235</v>
       </c>
       <c r="C15" t="n">
-        <v>38.49140289397449</v>
+        <v>41.12490891523056</v>
       </c>
       <c r="D15" t="n">
-        <v>1.442591604015421</v>
+        <v>1.599167498533026</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16255969176222</v>
+        <v>12.6405630854984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563654160629211</v>
+        <v>0.7563945865093007</v>
       </c>
       <c r="G15" t="n">
-        <v>24.171097421346</v>
+        <v>26.17152899867895</v>
       </c>
       <c r="H15" t="n">
-        <v>36.69280490789011</v>
+        <v>36.25728030805152</v>
       </c>
       <c r="I15" t="n">
-        <v>2.65329015078466</v>
+        <v>2.644126781878025</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727283850393258</v>
+        <v>4.727466165683128</v>
       </c>
       <c r="K15" t="n">
-        <v>17.3940069577454</v>
+        <v>15.20347257516766</v>
       </c>
       <c r="L15" t="n">
-        <v>44.02624173444427</v>
+        <v>43.58357246531492</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91165158616417</v>
+        <v>99.91195395571314</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.10024892427433</v>
+        <v>82.59189514522161</v>
       </c>
       <c r="C16" t="n">
-        <v>36.39538253614862</v>
+        <v>39.33026172042534</v>
       </c>
       <c r="D16" t="n">
-        <v>1.34814322853573</v>
+        <v>1.513270806715151</v>
       </c>
       <c r="E16" t="n">
-        <v>11.73511277508524</v>
+        <v>12.32916241822395</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757062010227472</v>
+        <v>0.7570678377142762</v>
       </c>
       <c r="G16" t="n">
-        <v>22.58858378501745</v>
+        <v>24.76576771171914</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72659808938284</v>
+        <v>36.28955216468812</v>
       </c>
       <c r="I16" t="n">
-        <v>2.213111472103898</v>
+        <v>2.205400220446745</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731637563921701</v>
+        <v>4.731673985714226</v>
       </c>
       <c r="K16" t="n">
-        <v>19.89975107572566</v>
+        <v>17.40810485477838</v>
       </c>
       <c r="L16" t="n">
-        <v>43.63116388393725</v>
+        <v>43.188185458633</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92629749581153</v>
+        <v>99.92655203383673</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.87243115764136</v>
+        <v>84.05028135988027</v>
       </c>
       <c r="C17" t="n">
-        <v>37.65553649154668</v>
+        <v>40.39358352904917</v>
       </c>
       <c r="D17" t="n">
-        <v>1.34938387898818</v>
+        <v>1.514612095858876</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54815501089967</v>
+        <v>13.04094861974346</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577587086981096</v>
+        <v>0.757738865574778</v>
       </c>
       <c r="G17" t="n">
-        <v>23.03489200503118</v>
+        <v>25.11608684238588</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18591704406644</v>
+        <v>36.65008541361632</v>
       </c>
       <c r="I17" t="n">
-        <v>2.260332580594608</v>
+        <v>2.234941612858576</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735991929363187</v>
+        <v>4.735867909842362</v>
       </c>
       <c r="K17" t="n">
-        <v>18.12756884235861</v>
+        <v>15.94971864011974</v>
       </c>
       <c r="L17" t="n">
-        <v>44.14161951990348</v>
+        <v>43.58226575002089</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92472485380878</v>
+        <v>99.92556791918979</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.51253547860404</v>
+        <v>81.97480780824026</v>
       </c>
       <c r="C18" t="n">
-        <v>35.64422900521792</v>
+        <v>38.66432142926445</v>
       </c>
       <c r="D18" t="n">
-        <v>1.264159657961134</v>
+        <v>1.436461075468072</v>
       </c>
       <c r="E18" t="n">
-        <v>12.06982335555867</v>
+        <v>12.67870500537129</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583575451851297</v>
+        <v>0.7583131563823546</v>
       </c>
       <c r="G18" t="n">
-        <v>21.58005712954494</v>
+        <v>23.82014590785673</v>
       </c>
       <c r="H18" t="n">
-        <v>37.21530408201622</v>
+        <v>36.67786253856817</v>
       </c>
       <c r="I18" t="n">
-        <v>1.885099050930878</v>
+        <v>1.863862897203916</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739734657407062</v>
+        <v>4.739457227389717</v>
       </c>
       <c r="K18" t="n">
-        <v>20.48746452139597</v>
+        <v>18.02519219175976</v>
       </c>
       <c r="L18" t="n">
-        <v>43.80551945725846</v>
+        <v>43.2484046675075</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93721298387234</v>
+        <v>99.93791828853172</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.56135939786745</v>
+        <v>81.09638904986542</v>
       </c>
       <c r="C19" t="n">
-        <v>34.98304092014261</v>
+        <v>38.07407623353749</v>
       </c>
       <c r="D19" t="n">
-        <v>1.230539887242164</v>
+        <v>1.404095221293052</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01082564671489</v>
+        <v>12.65206794207518</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588633538503753</v>
+        <v>0.7587975918021537</v>
       </c>
       <c r="G19" t="n">
-        <v>21.00614499097243</v>
+        <v>23.28343845225778</v>
       </c>
       <c r="H19" t="n">
-        <v>37.24012591362315</v>
+        <v>36.70129356516537</v>
       </c>
       <c r="I19" t="n">
-        <v>1.571963643899599</v>
+        <v>1.554211328508417</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742895961564848</v>
+        <v>4.742484948763461</v>
       </c>
       <c r="K19" t="n">
-        <v>21.43864060213253</v>
+        <v>18.90361095013459</v>
       </c>
       <c r="L19" t="n">
-        <v>43.52595461519901</v>
+        <v>42.97053884696115</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94763613747416</v>
+        <v>99.94822603063322</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.94133984711287</v>
+        <v>78.79995354243057</v>
       </c>
       <c r="C20" t="n">
-        <v>32.60468261190021</v>
+        <v>36.0178263845084</v>
       </c>
       <c r="D20" t="n">
-        <v>1.137054328961013</v>
+        <v>1.318463838293077</v>
       </c>
       <c r="E20" t="n">
-        <v>11.316803030403</v>
+        <v>12.09643884185481</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592999451834015</v>
+        <v>0.7592135460427375</v>
       </c>
       <c r="G20" t="n">
-        <v>19.41028352221744</v>
+        <v>21.86345424789199</v>
       </c>
       <c r="H20" t="n">
-        <v>37.26155100436208</v>
+        <v>36.72141231469525</v>
       </c>
       <c r="I20" t="n">
-        <v>1.310723358589674</v>
+        <v>1.295886090885588</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745624657396262</v>
+        <v>4.74508466276711</v>
       </c>
       <c r="K20" t="n">
-        <v>24.05866015288712</v>
+        <v>21.20004645756943</v>
       </c>
       <c r="L20" t="n">
-        <v>43.29299157843766</v>
+        <v>42.73895462101918</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95633434322501</v>
+        <v>99.95682746309701</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.87399213649114</v>
+        <v>84.0165877786705</v>
       </c>
       <c r="C21" t="n">
-        <v>36.21614162124967</v>
+        <v>39.08297785984971</v>
       </c>
       <c r="D21" t="n">
-        <v>1.137958647386418</v>
+        <v>1.319535354661547</v>
       </c>
       <c r="E21" t="n">
-        <v>13.28637194532697</v>
+        <v>13.80091165100807</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599038291961081</v>
+        <v>0.7598305593563542</v>
       </c>
       <c r="G21" t="n">
-        <v>21.06071050568271</v>
+        <v>23.23446305485483</v>
       </c>
       <c r="H21" t="n">
-        <v>38.92617540099379</v>
+        <v>38.10449619327419</v>
       </c>
       <c r="I21" t="n">
-        <v>1.953472875429456</v>
+        <v>2.048409969538295</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749398932475679</v>
+        <v>4.748940995977215</v>
       </c>
       <c r="K21" t="n">
-        <v>18.12600786350886</v>
+        <v>15.9834122213295</v>
       </c>
       <c r="L21" t="n">
-        <v>45.59278649923302</v>
+        <v>44.86538503290939</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93493598399155</v>
+        <v>99.93177511408859</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_29_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.18346592598928</v>
+        <v>45.39223477938769</v>
       </c>
       <c r="M2" t="n">
-        <v>99.89562454510477</v>
+        <v>99.38596360794824</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09958967456832</v>
+        <v>87.98180940248983</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95210266488046</v>
+        <v>45.88811480388691</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228898145836894</v>
+        <v>2.228644626321752</v>
       </c>
       <c r="E3" t="n">
-        <v>5.723712577408175</v>
+        <v>5.680763139143759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742966048612298</v>
+        <v>0.7428815421072509</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98048840608374</v>
+        <v>33.95950255480983</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1764382361657</v>
+        <v>34.17255093693354</v>
       </c>
       <c r="I3" t="n">
-        <v>6.603548456634649</v>
+        <v>6.554456965003378</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643537803826862</v>
+        <v>4.643009638170318</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90041032543168</v>
+        <v>12.01819059751017</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91047129969792</v>
+        <v>48.85841412768023</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7629842900101</v>
+        <v>106.7647195290773</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.322277954222</v>
+        <v>87.05398687902834</v>
       </c>
       <c r="C4" t="n">
-        <v>42.81591296546071</v>
+        <v>42.59431058406046</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192186149183816</v>
+        <v>2.183824803760729</v>
       </c>
       <c r="E4" t="n">
-        <v>6.548527959233774</v>
+        <v>6.47876761760377</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445300316264744</v>
+        <v>0.7444384910470189</v>
       </c>
       <c r="G4" t="n">
-        <v>33.42079859748296</v>
+        <v>33.2765498485817</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24838145481782</v>
+        <v>34.24417058816287</v>
       </c>
       <c r="I4" t="n">
-        <v>5.514541064211704</v>
+        <v>5.473494960828372</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653312697665465</v>
+        <v>4.652740569043868</v>
       </c>
       <c r="K4" t="n">
-        <v>12.677722045778</v>
+        <v>12.94601312097167</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3229330871881</v>
+        <v>44.27760804594001</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81656809842681</v>
+        <v>99.81793175097214</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.3807766777357</v>
+        <v>85.82591671033174</v>
       </c>
       <c r="C5" t="n">
-        <v>42.73044994218125</v>
+        <v>42.21571822574501</v>
       </c>
       <c r="D5" t="n">
-        <v>2.147040241061844</v>
+        <v>2.123639668945055</v>
       </c>
       <c r="E5" t="n">
-        <v>7.180936598196145</v>
+        <v>7.061772715874334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458526751857869</v>
+        <v>0.7457596121526389</v>
       </c>
       <c r="G5" t="n">
-        <v>32.73253026616143</v>
+        <v>32.35946454238476</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30922305854619</v>
+        <v>34.30494215902139</v>
       </c>
       <c r="I5" t="n">
-        <v>4.603614618673141</v>
+        <v>4.569340435999584</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661579219911168</v>
+        <v>4.660997575953992</v>
       </c>
       <c r="K5" t="n">
-        <v>13.61922332226429</v>
+        <v>14.17408328966827</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49714503932637</v>
+        <v>43.45815695789705</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84681830377191</v>
+        <v>99.84795847331031</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.29538258383789</v>
+        <v>84.28247498933278</v>
       </c>
       <c r="C6" t="n">
-        <v>42.36035660596753</v>
+        <v>41.38182543446887</v>
       </c>
       <c r="D6" t="n">
-        <v>2.094775277753918</v>
+        <v>2.047827871738199</v>
       </c>
       <c r="E6" t="n">
-        <v>7.646483479641973</v>
+        <v>7.445262329235017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469725657613755</v>
+        <v>0.7468843909426486</v>
       </c>
       <c r="G6" t="n">
-        <v>31.93572894841323</v>
+        <v>31.20426425135403</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36073802502327</v>
+        <v>34.35668198336183</v>
       </c>
       <c r="I6" t="n">
-        <v>3.84210575123552</v>
+        <v>3.813526719309491</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668578536008597</v>
+        <v>4.668027443391553</v>
       </c>
       <c r="K6" t="n">
-        <v>14.70461741616213</v>
+        <v>15.71752501066723</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80714779401831</v>
+        <v>42.7737234316417</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87212181614797</v>
+        <v>99.8730738767778</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84.05996451866346</v>
+        <v>82.54776900182026</v>
       </c>
       <c r="C7" t="n">
-        <v>41.72216800517882</v>
+        <v>40.23918934455037</v>
       </c>
       <c r="D7" t="n">
-        <v>2.035264537146945</v>
+        <v>1.963059292358931</v>
       </c>
       <c r="E7" t="n">
-        <v>7.963557713905673</v>
+        <v>7.667407315108686</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479221511141672</v>
+        <v>0.7478440788269992</v>
       </c>
       <c r="G7" t="n">
-        <v>31.02846271239893</v>
+        <v>29.91258286168852</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40441895125168</v>
+        <v>34.40082762604196</v>
       </c>
       <c r="I7" t="n">
-        <v>3.205825008382536</v>
+        <v>3.182022335126414</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674513444463544</v>
+        <v>4.674025492668744</v>
       </c>
       <c r="K7" t="n">
-        <v>15.94003548133652</v>
+        <v>17.45223099817974</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23107135372813</v>
+        <v>42.20264835951129</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89327484024346</v>
+        <v>99.89406870224141</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89.09527247247495</v>
+        <v>87.40269037402423</v>
       </c>
       <c r="C8" t="n">
-        <v>44.07205847380722</v>
+        <v>42.54252675958104</v>
       </c>
       <c r="D8" t="n">
-        <v>2.039654285083474</v>
+        <v>1.967259801123285</v>
       </c>
       <c r="E8" t="n">
-        <v>9.835545065118287</v>
+        <v>9.499818409313908</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495353024562231</v>
+        <v>0.749444298249668</v>
       </c>
       <c r="G8" t="n">
-        <v>31.54238037238025</v>
+        <v>30.41703576339458</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47862391298625</v>
+        <v>34.47443771948473</v>
       </c>
       <c r="I8" t="n">
-        <v>5.764937894099072</v>
+        <v>5.610667518397648</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684595640351394</v>
+        <v>4.684026864060424</v>
       </c>
       <c r="K8" t="n">
-        <v>10.90472752752505</v>
+        <v>12.59730962597576</v>
       </c>
       <c r="L8" t="n">
-        <v>44.83146297921763</v>
+        <v>44.67354069522602</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80824898054992</v>
+        <v>99.81337708078283</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.59291527972157</v>
+        <v>85.15798904342346</v>
       </c>
       <c r="C9" t="n">
-        <v>43.46544365090971</v>
+        <v>41.16811631903587</v>
       </c>
       <c r="D9" t="n">
-        <v>1.972683584879506</v>
+        <v>1.865241836247807</v>
       </c>
       <c r="E9" t="n">
-        <v>10.31475375598336</v>
+        <v>9.787865916350043</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509081109158587</v>
+        <v>0.7508184083998933</v>
       </c>
       <c r="G9" t="n">
-        <v>30.50670716291194</v>
+        <v>28.83967212064932</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54177310212949</v>
+        <v>34.53764678639509</v>
       </c>
       <c r="I9" t="n">
-        <v>4.81291386967729</v>
+        <v>4.684128922881969</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693175693224116</v>
+        <v>4.692615052499333</v>
       </c>
       <c r="K9" t="n">
-        <v>12.40708472027844</v>
+        <v>14.84201095657655</v>
       </c>
       <c r="L9" t="n">
-        <v>43.96733446508687</v>
+        <v>43.83402084887652</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83986283627502</v>
+        <v>99.84414812448894</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.84366788823765</v>
+        <v>82.82262547389226</v>
       </c>
       <c r="C10" t="n">
-        <v>42.46426548288416</v>
+        <v>39.55880817362726</v>
       </c>
       <c r="D10" t="n">
-        <v>1.894999703168032</v>
+        <v>1.760432308989732</v>
       </c>
       <c r="E10" t="n">
-        <v>10.57806377012155</v>
+        <v>9.889474518284649</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520793916819981</v>
+        <v>0.7519998032476306</v>
       </c>
       <c r="G10" t="n">
-        <v>29.30535918758777</v>
+        <v>27.21914638371664</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5956520173719</v>
+        <v>34.59199094939101</v>
       </c>
       <c r="I10" t="n">
-        <v>4.017017620293917</v>
+        <v>3.90958273996491</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700496198012488</v>
+        <v>4.699998770297691</v>
       </c>
       <c r="K10" t="n">
-        <v>14.15633211176235</v>
+        <v>17.17737452610774</v>
       </c>
       <c r="L10" t="n">
-        <v>43.24571035341802</v>
+        <v>43.13370260796274</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86630794806453</v>
+        <v>99.86988530769773</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83.88843680217843</v>
+        <v>80.31106401988089</v>
       </c>
       <c r="C11" t="n">
-        <v>41.13319008042984</v>
+        <v>37.65248916300016</v>
       </c>
       <c r="D11" t="n">
-        <v>1.808719536053369</v>
+        <v>1.648909988883618</v>
       </c>
       <c r="E11" t="n">
-        <v>10.65510210595368</v>
+        <v>9.80671515768603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75308109908181</v>
+        <v>0.7530180614595154</v>
       </c>
       <c r="G11" t="n">
-        <v>27.97107333844845</v>
+        <v>25.4948299527361</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64173055776325</v>
+        <v>34.63883082713772</v>
       </c>
       <c r="I11" t="n">
-        <v>3.351973295616575</v>
+        <v>3.262397147855939</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706756869261311</v>
+        <v>4.706362884121972</v>
       </c>
       <c r="K11" t="n">
-        <v>16.11156319782156</v>
+        <v>19.68893598011913</v>
       </c>
       <c r="L11" t="n">
-        <v>42.64366289896265</v>
+        <v>42.54997533632613</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88841617721405</v>
+        <v>99.89140047944541</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>81.84770410926124</v>
+        <v>77.90822354576294</v>
       </c>
       <c r="C12" t="n">
-        <v>39.61279523323353</v>
+        <v>35.75374340162731</v>
       </c>
       <c r="D12" t="n">
-        <v>1.719390184326566</v>
+        <v>1.543478858075456</v>
       </c>
       <c r="E12" t="n">
-        <v>10.59494815337181</v>
+        <v>9.63331320769843</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539387837213849</v>
+        <v>0.7538949853072572</v>
       </c>
       <c r="G12" t="n">
-        <v>26.58963315459414</v>
+        <v>23.86469321404206</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68118405118369</v>
+        <v>34.67916932413384</v>
       </c>
       <c r="I12" t="n">
-        <v>2.796492383804985</v>
+        <v>2.721830298335549</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712117398258655</v>
+        <v>4.711843658170357</v>
       </c>
       <c r="K12" t="n">
-        <v>18.15229589073875</v>
+        <v>22.09177645423707</v>
       </c>
       <c r="L12" t="n">
-        <v>42.14179850670504</v>
+        <v>42.06385800113964</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90688963067733</v>
+        <v>99.909377857004</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79.56161893090979</v>
+        <v>75.59389327706131</v>
       </c>
       <c r="C13" t="n">
-        <v>37.76022681763538</v>
+        <v>33.85908198230152</v>
       </c>
       <c r="D13" t="n">
-        <v>1.619936568458219</v>
+        <v>1.442982340761816</v>
       </c>
       <c r="E13" t="n">
-        <v>10.37089247254009</v>
+        <v>9.384494843571989</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754675614647375</v>
+        <v>0.7546497598928986</v>
       </c>
       <c r="G13" t="n">
-        <v>25.05162555984157</v>
+        <v>22.31085362484281</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71507827377923</v>
+        <v>34.71388895507334</v>
       </c>
       <c r="I13" t="n">
-        <v>2.332687850097208</v>
+        <v>2.270462753587843</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716722591546093</v>
+        <v>4.716560999330616</v>
       </c>
       <c r="K13" t="n">
-        <v>20.43838106909019</v>
+        <v>24.40610672293868</v>
       </c>
       <c r="L13" t="n">
-        <v>41.72371176927984</v>
+        <v>41.65920489758382</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92231965600541</v>
+        <v>99.92439360282403</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>85.40723340173609</v>
+        <v>82.80929335685003</v>
       </c>
       <c r="C14" t="n">
-        <v>41.24436225303067</v>
+        <v>38.45138797875344</v>
       </c>
       <c r="D14" t="n">
-        <v>1.62194055338316</v>
+        <v>1.444603344215208</v>
       </c>
       <c r="E14" t="n">
-        <v>12.37360845240875</v>
+        <v>11.90936494492727</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755609205865958</v>
+        <v>0.7554975109930555</v>
       </c>
       <c r="G14" t="n">
-        <v>26.54422645904226</v>
+        <v>24.38511732449085</v>
       </c>
       <c r="H14" t="n">
-        <v>36.21963360004742</v>
+        <v>36.80208585579732</v>
       </c>
       <c r="I14" t="n">
-        <v>3.169657594326316</v>
+        <v>2.79076493271975</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722557536662237</v>
+        <v>4.721859443706596</v>
       </c>
       <c r="K14" t="n">
-        <v>14.59276659826389</v>
+        <v>17.19070664314997</v>
       </c>
       <c r="L14" t="n">
-        <v>44.05734643766654</v>
+        <v>44.26498426515447</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8944752889611</v>
+        <v>99.90707888705788</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.79652742483235</v>
+        <v>82.08987845665501</v>
       </c>
       <c r="C15" t="n">
-        <v>41.12490891523056</v>
+        <v>38.16277446508687</v>
       </c>
       <c r="D15" t="n">
-        <v>1.599167498533026</v>
+        <v>1.418404537762704</v>
       </c>
       <c r="E15" t="n">
-        <v>12.6405630854984</v>
+        <v>12.08135360856929</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563945865093007</v>
+        <v>0.7562116364249487</v>
       </c>
       <c r="G15" t="n">
-        <v>26.17152899867895</v>
+        <v>23.94287761096381</v>
       </c>
       <c r="H15" t="n">
-        <v>36.25728030805152</v>
+        <v>36.83687260899495</v>
       </c>
       <c r="I15" t="n">
-        <v>2.644126781878025</v>
+        <v>2.327835726283378</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727466165683128</v>
+        <v>4.726322727655929</v>
       </c>
       <c r="K15" t="n">
-        <v>15.20347257516766</v>
+        <v>17.91012154334499</v>
       </c>
       <c r="L15" t="n">
-        <v>43.58357246531492</v>
+        <v>43.84958274343704</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91195395571314</v>
+        <v>99.92247875186889</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.59189514522161</v>
+        <v>79.59568950915373</v>
       </c>
       <c r="C16" t="n">
-        <v>39.33026172042534</v>
+        <v>36.02796896375883</v>
       </c>
       <c r="D16" t="n">
-        <v>1.513270806715151</v>
+        <v>1.324995900979583</v>
       </c>
       <c r="E16" t="n">
-        <v>12.32916241822395</v>
+        <v>11.60931280575757</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570678377142762</v>
+        <v>0.7568264686068464</v>
       </c>
       <c r="G16" t="n">
-        <v>24.76576771171914</v>
+        <v>22.36612605753681</v>
       </c>
       <c r="H16" t="n">
-        <v>36.28955216468812</v>
+        <v>36.86682255114018</v>
       </c>
       <c r="I16" t="n">
-        <v>2.205400220446745</v>
+        <v>1.941440296339969</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731673985714226</v>
+        <v>4.730165428792789</v>
       </c>
       <c r="K16" t="n">
-        <v>17.40810485477838</v>
+        <v>20.40431049084626</v>
       </c>
       <c r="L16" t="n">
-        <v>43.188185458633</v>
+        <v>43.50305844188703</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92655203383673</v>
+        <v>99.93533789649211</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>84.05028135988027</v>
+        <v>81.37057154870745</v>
       </c>
       <c r="C17" t="n">
-        <v>40.39358352904917</v>
+        <v>37.33153523463943</v>
       </c>
       <c r="D17" t="n">
-        <v>1.514612095858876</v>
+        <v>1.326027940481599</v>
       </c>
       <c r="E17" t="n">
-        <v>13.04094861974346</v>
+        <v>12.41443744353845</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757738865574778</v>
+        <v>0.7574159608544803</v>
       </c>
       <c r="G17" t="n">
-        <v>25.11608684238588</v>
+        <v>22.86273142804604</v>
       </c>
       <c r="H17" t="n">
-        <v>36.65008541361632</v>
+        <v>37.37472251627953</v>
       </c>
       <c r="I17" t="n">
-        <v>2.234941612858576</v>
+        <v>1.901386504166857</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735867909842362</v>
+        <v>4.733849755340501</v>
       </c>
       <c r="K17" t="n">
-        <v>15.94971864011974</v>
+        <v>18.62942845129254</v>
       </c>
       <c r="L17" t="n">
-        <v>43.58226575002089</v>
+        <v>43.97570609184854</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92556791918979</v>
+        <v>99.93666977778051</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.97480780824026</v>
+        <v>78.94446680449569</v>
       </c>
       <c r="C18" t="n">
-        <v>38.66432142926445</v>
+        <v>35.19858948762087</v>
       </c>
       <c r="D18" t="n">
-        <v>1.436461075468072</v>
+        <v>1.238966090119051</v>
       </c>
       <c r="E18" t="n">
-        <v>12.67870500537129</v>
+        <v>11.86361189758506</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583131563823546</v>
+        <v>0.7579230348240216</v>
       </c>
       <c r="G18" t="n">
-        <v>23.82014590785673</v>
+        <v>21.36165317644845</v>
       </c>
       <c r="H18" t="n">
-        <v>36.67786253856817</v>
+        <v>37.39974410268161</v>
       </c>
       <c r="I18" t="n">
-        <v>1.863862897203916</v>
+        <v>1.585549535187372</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739457227389717</v>
+        <v>4.737018967650133</v>
       </c>
       <c r="K18" t="n">
-        <v>18.02519219175976</v>
+        <v>21.0555331955043</v>
       </c>
       <c r="L18" t="n">
-        <v>43.2484046675075</v>
+        <v>43.69306102509241</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93791828853172</v>
+        <v>99.94718370821758</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>81.09638904986542</v>
+        <v>77.99062037000358</v>
       </c>
       <c r="C19" t="n">
-        <v>38.07407623353749</v>
+        <v>34.48626577610825</v>
       </c>
       <c r="D19" t="n">
-        <v>1.404095221293052</v>
+        <v>1.205263479555823</v>
       </c>
       <c r="E19" t="n">
-        <v>12.65206794207518</v>
+        <v>11.76159960579503</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587975918021537</v>
+        <v>0.7583520011178615</v>
       </c>
       <c r="G19" t="n">
-        <v>23.28343845225778</v>
+        <v>20.78056909050433</v>
       </c>
       <c r="H19" t="n">
-        <v>36.70129356516537</v>
+        <v>37.42091146253367</v>
       </c>
       <c r="I19" t="n">
-        <v>1.554211328508417</v>
+        <v>1.324224723510229</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742484948763461</v>
+        <v>4.739700006986634</v>
       </c>
       <c r="K19" t="n">
-        <v>18.90361095013459</v>
+        <v>22.00937962999642</v>
       </c>
       <c r="L19" t="n">
-        <v>42.97053884696115</v>
+        <v>43.4602387382965</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94822603063322</v>
+        <v>99.95588414440117</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.79995354243057</v>
+        <v>75.41126480915889</v>
       </c>
       <c r="C20" t="n">
-        <v>36.0178263845084</v>
+        <v>32.11034871661589</v>
       </c>
       <c r="D20" t="n">
-        <v>1.318463838293077</v>
+        <v>1.113687020517836</v>
       </c>
       <c r="E20" t="n">
-        <v>12.09643884185481</v>
+        <v>11.05195785609773</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592135460427375</v>
+        <v>0.7587220897069713</v>
       </c>
       <c r="G20" t="n">
-        <v>21.86345424789199</v>
+        <v>19.20165214298017</v>
       </c>
       <c r="H20" t="n">
-        <v>36.72141231469525</v>
+        <v>37.43917349956391</v>
       </c>
       <c r="I20" t="n">
-        <v>1.295886090885588</v>
+        <v>1.104059139623701</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74508466276711</v>
+        <v>4.74201306066857</v>
       </c>
       <c r="K20" t="n">
-        <v>21.20004645756943</v>
+        <v>24.5887351908411</v>
       </c>
       <c r="L20" t="n">
-        <v>42.73895462101918</v>
+        <v>43.2641320724455</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95682746309701</v>
+        <v>99.96321597990249</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>84.0165877786705</v>
+        <v>81.36284519427505</v>
       </c>
       <c r="C21" t="n">
-        <v>39.08297785984971</v>
+        <v>35.88265425644647</v>
       </c>
       <c r="D21" t="n">
-        <v>1.319535354661547</v>
+        <v>1.114369762610303</v>
       </c>
       <c r="E21" t="n">
-        <v>13.80091165100807</v>
+        <v>13.06290034001185</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598305593563542</v>
+        <v>0.7591872217392064</v>
       </c>
       <c r="G21" t="n">
-        <v>23.23446305485483</v>
+        <v>20.96819467292161</v>
       </c>
       <c r="H21" t="n">
-        <v>38.10449619327419</v>
+        <v>39.21689648080181</v>
       </c>
       <c r="I21" t="n">
-        <v>2.048409969538295</v>
+        <v>1.496376580320228</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748940995977215</v>
+        <v>4.744920135870039</v>
       </c>
       <c r="K21" t="n">
-        <v>15.9834122213295</v>
+        <v>18.63715480572496</v>
       </c>
       <c r="L21" t="n">
-        <v>44.86538503290939</v>
+        <v>45.43034227803824</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93177511408859</v>
+        <v>99.95015134020967</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_29_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.39223477938769</v>
+        <v>43.44208725204351</v>
       </c>
       <c r="M2" t="n">
-        <v>99.38596360794824</v>
+        <v>97.56821532001541</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98180940248983</v>
+        <v>81.55931804855146</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88811480388691</v>
+        <v>43.31487360410701</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228644626321752</v>
+        <v>2.184501463079464</v>
       </c>
       <c r="E3" t="n">
-        <v>5.680763139143759</v>
+        <v>4.160510162200095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428815421072509</v>
+        <v>0.7376910928786931</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95950255480983</v>
+        <v>32.85854284048694</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17255093693354</v>
+        <v>33.93379027241988</v>
       </c>
       <c r="I3" t="n">
-        <v>6.554456965003378</v>
+        <v>3.073712886994555</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643009638170318</v>
+        <v>4.610569330491831</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01819059751017</v>
+        <v>18.44068195144855</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85841412768023</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7647195290773</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05398687902834</v>
+        <v>88.77182973657089</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59431058406046</v>
+        <v>42.9846729734805</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183824803760729</v>
+        <v>2.19026602520298</v>
       </c>
       <c r="E4" t="n">
-        <v>6.47876761760377</v>
+        <v>6.59622006338556</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444384910470189</v>
+        <v>0.7396377457900027</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2765498485817</v>
+        <v>33.571979055219</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24417058816287</v>
+        <v>34.02333630634013</v>
       </c>
       <c r="I4" t="n">
-        <v>5.473494960828372</v>
+        <v>7.027654629445703</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652740569043868</v>
+        <v>4.622735911187517</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94601312097167</v>
+        <v>11.2281702634291</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27760804594001</v>
+        <v>45.55351814502012</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81793175097214</v>
+        <v>99.76636138192973</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82591671033174</v>
+        <v>87.73966063572907</v>
       </c>
       <c r="C5" t="n">
-        <v>42.21571822574501</v>
+        <v>43.04199693173427</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123639668945055</v>
+        <v>2.141659753964436</v>
       </c>
       <c r="E5" t="n">
-        <v>7.061772715874334</v>
+        <v>7.42807672189803</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457596121526389</v>
+        <v>0.7412870408835365</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35946454238476</v>
+        <v>32.82695141876034</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30494215902139</v>
+        <v>34.09920388064268</v>
       </c>
       <c r="I5" t="n">
-        <v>4.569340435999584</v>
+        <v>5.86943781405793</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660997575953992</v>
+        <v>4.633044005522103</v>
       </c>
       <c r="K5" t="n">
-        <v>14.17408328966827</v>
+        <v>12.26033936427095</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45815695789705</v>
+        <v>44.50245107539907</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84795847331031</v>
+        <v>99.80478737140427</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.28247498933278</v>
+        <v>86.40842606240915</v>
       </c>
       <c r="C6" t="n">
-        <v>41.38182543446887</v>
+        <v>42.62194005858335</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047827871738199</v>
+        <v>2.078334229814253</v>
       </c>
       <c r="E6" t="n">
-        <v>7.445262329235017</v>
+        <v>8.025180894450129</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468843909426486</v>
+        <v>0.7426883841850982</v>
       </c>
       <c r="G6" t="n">
-        <v>31.20426425135403</v>
+        <v>31.85630988665068</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35668198336183</v>
+        <v>34.16366567251452</v>
       </c>
       <c r="I6" t="n">
-        <v>3.813526719309491</v>
+        <v>4.900444593637589</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668027443391553</v>
+        <v>4.641802401156863</v>
       </c>
       <c r="K6" t="n">
-        <v>15.71752501066723</v>
+        <v>13.59157393759088</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7737234316417</v>
+        <v>43.62344606454639</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8730738767778</v>
+        <v>99.83696006072061</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.54776900182026</v>
+        <v>84.80129398883838</v>
       </c>
       <c r="C7" t="n">
-        <v>40.23918934455037</v>
+        <v>41.7759986262013</v>
       </c>
       <c r="D7" t="n">
-        <v>1.963059292358931</v>
+        <v>2.001944053786712</v>
       </c>
       <c r="E7" t="n">
-        <v>7.667407315108686</v>
+        <v>8.411923095400613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478440788269992</v>
+        <v>0.7438824680406042</v>
       </c>
       <c r="G7" t="n">
-        <v>29.91258286168852</v>
+        <v>30.68541586733473</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40082762604196</v>
+        <v>34.2185935298678</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182022335126414</v>
+        <v>4.090269549154148</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674025492668744</v>
+        <v>4.649265425253776</v>
       </c>
       <c r="K7" t="n">
-        <v>17.45223099817974</v>
+        <v>15.19870601116162</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20264835951129</v>
+        <v>42.88917190170271</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89406870224141</v>
+        <v>99.86387653906563</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.40269037402423</v>
+        <v>83.10854586153056</v>
       </c>
       <c r="C8" t="n">
-        <v>42.54252675958104</v>
+        <v>40.71851035019293</v>
       </c>
       <c r="D8" t="n">
-        <v>1.967259801123285</v>
+        <v>1.922118124414173</v>
       </c>
       <c r="E8" t="n">
-        <v>9.499818409313908</v>
+        <v>8.645375044272614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749444298249668</v>
+        <v>0.7449008300817551</v>
       </c>
       <c r="G8" t="n">
-        <v>30.41703576339458</v>
+        <v>29.46185927734932</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47443771948473</v>
+        <v>34.26543818376074</v>
       </c>
       <c r="I8" t="n">
-        <v>5.610667518397648</v>
+        <v>3.413224213640988</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684026864060424</v>
+        <v>4.655630188010969</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59730962597576</v>
+        <v>16.89145413846944</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67354069522602</v>
+        <v>42.27641691275002</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81337708078283</v>
+        <v>99.88638140141239</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.15798904342346</v>
+        <v>81.33851215959305</v>
       </c>
       <c r="C9" t="n">
-        <v>41.16811631903587</v>
+        <v>39.47827849274159</v>
       </c>
       <c r="D9" t="n">
-        <v>1.865241836247807</v>
+        <v>1.839269080486498</v>
       </c>
       <c r="E9" t="n">
-        <v>9.787865916350043</v>
+        <v>8.747345652428091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508184083998933</v>
+        <v>0.7457701328838436</v>
       </c>
       <c r="G9" t="n">
-        <v>28.83967212064932</v>
+        <v>28.19196496520654</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53764678639509</v>
+        <v>34.30542611265681</v>
       </c>
       <c r="I9" t="n">
-        <v>4.684128922881969</v>
+        <v>2.847672885407241</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692615052499333</v>
+        <v>4.661063330524023</v>
       </c>
       <c r="K9" t="n">
-        <v>14.84201095657655</v>
+        <v>18.66148784040695</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83402084887652</v>
+        <v>41.76542188313919</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84414812448894</v>
+        <v>99.90518821628774</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.82262547389226</v>
+        <v>86.1377813208973</v>
       </c>
       <c r="C10" t="n">
-        <v>39.55880817362726</v>
+        <v>42.84088430053724</v>
       </c>
       <c r="D10" t="n">
-        <v>1.760432308989732</v>
+        <v>1.841273270857188</v>
       </c>
       <c r="E10" t="n">
-        <v>9.889474518284649</v>
+        <v>10.65160522928254</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519998032476306</v>
+        <v>0.7465827738045939</v>
       </c>
       <c r="G10" t="n">
-        <v>27.21914638371664</v>
+        <v>29.64810531397431</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59199094939101</v>
+        <v>35.76822809679555</v>
       </c>
       <c r="I10" t="n">
-        <v>3.90958273996491</v>
+        <v>2.815844299904396</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699998770297691</v>
+        <v>4.666142336278712</v>
       </c>
       <c r="K10" t="n">
-        <v>17.17737452610774</v>
+        <v>13.86221867910271</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13370260796274</v>
+        <v>43.20313771009994</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86988530769773</v>
+        <v>99.90624068973989</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.31106401988089</v>
+        <v>85.9235541543536</v>
       </c>
       <c r="C11" t="n">
-        <v>37.65248916300016</v>
+        <v>42.93445969223067</v>
       </c>
       <c r="D11" t="n">
-        <v>1.648909988883618</v>
+        <v>1.822327671112638</v>
       </c>
       <c r="E11" t="n">
-        <v>9.80671515768603</v>
+        <v>11.00354139675069</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530180614595154</v>
+        <v>0.7472830958519994</v>
       </c>
       <c r="G11" t="n">
-        <v>25.4948299527361</v>
+        <v>29.40158162774573</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63883082713772</v>
+        <v>35.86031757740269</v>
       </c>
       <c r="I11" t="n">
-        <v>3.262397147855939</v>
+        <v>2.417983436414844</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706362884121972</v>
+        <v>4.670519349074996</v>
       </c>
       <c r="K11" t="n">
-        <v>19.68893598011913</v>
+        <v>14.07644584564641</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54997533632613</v>
+        <v>42.90857054862917</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89140047944541</v>
+        <v>99.91947608650624</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.90822354576294</v>
+        <v>84.09091589735904</v>
       </c>
       <c r="C12" t="n">
-        <v>35.75374340162731</v>
+        <v>41.47792656730189</v>
       </c>
       <c r="D12" t="n">
-        <v>1.543478858075456</v>
+        <v>1.744633575519517</v>
       </c>
       <c r="E12" t="n">
-        <v>9.63331320769843</v>
+        <v>10.87050999619239</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538949853072572</v>
+        <v>0.7478804528012523</v>
       </c>
       <c r="G12" t="n">
-        <v>23.86469321404206</v>
+        <v>28.14805882293626</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67916932413384</v>
+        <v>35.88898329997313</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721830298335549</v>
+        <v>2.016596919928645</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711843658170357</v>
+        <v>4.674252830007827</v>
       </c>
       <c r="K12" t="n">
-        <v>22.09177645423707</v>
+        <v>15.90908410264097</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06385800113964</v>
+        <v>42.54582312349005</v>
       </c>
       <c r="M12" t="n">
-        <v>99.909377857004</v>
+        <v>99.93283379343291</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.59389327706131</v>
+        <v>85.25285357524328</v>
       </c>
       <c r="C13" t="n">
-        <v>33.85908198230152</v>
+        <v>42.45749346420602</v>
       </c>
       <c r="D13" t="n">
-        <v>1.442982340761816</v>
+        <v>1.745897469688958</v>
       </c>
       <c r="E13" t="n">
-        <v>9.384494843571989</v>
+        <v>11.50633610989011</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546497598928986</v>
+        <v>0.7484222523842697</v>
       </c>
       <c r="G13" t="n">
-        <v>22.31085362484281</v>
+        <v>28.48759582650852</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71388895507334</v>
+        <v>36.23412819132762</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270462753587843</v>
+        <v>1.852834648042139</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716560999330616</v>
+        <v>4.677639077401686</v>
       </c>
       <c r="K13" t="n">
-        <v>24.40610672293868</v>
+        <v>14.7471464247567</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65920489758382</v>
+        <v>42.73364366638191</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92439360282403</v>
+        <v>99.93828355534464</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.80929335685003</v>
+        <v>83.32210927016335</v>
       </c>
       <c r="C14" t="n">
-        <v>38.45138797875344</v>
+        <v>40.81484549895332</v>
       </c>
       <c r="D14" t="n">
-        <v>1.444603344215208</v>
+        <v>1.666167299962511</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90936494492727</v>
+        <v>11.23837167969793</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554975109930555</v>
+        <v>0.7488848346118828</v>
       </c>
       <c r="G14" t="n">
-        <v>24.38511732449085</v>
+        <v>27.18664838269865</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80208585579732</v>
+        <v>36.25652365549369</v>
       </c>
       <c r="I14" t="n">
-        <v>2.79076493271975</v>
+        <v>1.544983201374419</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721859443706596</v>
+        <v>4.680530216324268</v>
       </c>
       <c r="K14" t="n">
-        <v>17.19070664314997</v>
+        <v>16.67789072983664</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26498426515447</v>
+        <v>42.45579614209775</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90707888705788</v>
+        <v>99.94853237088772</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.08987845665501</v>
+        <v>82.43599360978723</v>
       </c>
       <c r="C15" t="n">
-        <v>38.16277446508687</v>
+        <v>40.13816253552403</v>
       </c>
       <c r="D15" t="n">
-        <v>1.418404537762704</v>
+        <v>1.628742136357962</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08135360856929</v>
+        <v>11.20553443245664</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562116364249487</v>
+        <v>0.7492838179939962</v>
       </c>
       <c r="G15" t="n">
-        <v>23.94287761096381</v>
+        <v>26.57598655803992</v>
       </c>
       <c r="H15" t="n">
-        <v>36.83687260899495</v>
+        <v>36.27584004402657</v>
       </c>
       <c r="I15" t="n">
-        <v>2.327835726283378</v>
+        <v>1.317582758449668</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726322727655929</v>
+        <v>4.683023862462477</v>
       </c>
       <c r="K15" t="n">
-        <v>17.91012154334499</v>
+        <v>17.56400639021277</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84958274343704</v>
+        <v>42.25393503547464</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92247875186889</v>
+        <v>99.95610396121145</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.59568950915373</v>
+        <v>80.07134627186132</v>
       </c>
       <c r="C16" t="n">
-        <v>36.02796896375883</v>
+        <v>37.97789721226283</v>
       </c>
       <c r="D16" t="n">
-        <v>1.324995900979583</v>
+        <v>1.531716430973702</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60931280575757</v>
+        <v>10.72109146592564</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568264686068464</v>
+        <v>0.749626462032941</v>
       </c>
       <c r="G16" t="n">
-        <v>22.36612605753681</v>
+        <v>24.99282997080852</v>
       </c>
       <c r="H16" t="n">
-        <v>36.86682255114018</v>
+        <v>36.29242881860078</v>
       </c>
       <c r="I16" t="n">
-        <v>1.941440296339969</v>
+        <v>1.098487735813861</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730165428792789</v>
+        <v>4.685165387705882</v>
       </c>
       <c r="K16" t="n">
-        <v>20.40431049084626</v>
+        <v>19.92865372813868</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50305844188703</v>
+        <v>42.05684953853044</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93533789649211</v>
+        <v>99.96340047893196</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.37057154870745</v>
+        <v>84.67112879056889</v>
       </c>
       <c r="C17" t="n">
-        <v>37.33153523463943</v>
+        <v>41.05301387766391</v>
       </c>
       <c r="D17" t="n">
-        <v>1.326027940481599</v>
+        <v>1.532422366040488</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41443744353845</v>
+        <v>12.35316972777371</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574159608544803</v>
+        <v>0.7499719487012552</v>
       </c>
       <c r="G17" t="n">
-        <v>22.86273142804604</v>
+        <v>26.43637028380817</v>
       </c>
       <c r="H17" t="n">
-        <v>37.37472251627953</v>
+        <v>37.74117687299822</v>
       </c>
       <c r="I17" t="n">
-        <v>1.901386504166857</v>
+        <v>1.170692911864213</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733849755340501</v>
+        <v>4.687324679382845</v>
       </c>
       <c r="K17" t="n">
-        <v>18.62942845129254</v>
+        <v>15.3288712094311</v>
       </c>
       <c r="L17" t="n">
-        <v>43.97570609184854</v>
+        <v>43.57910979246159</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93666977778051</v>
+        <v>99.96099487955661</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.94446680449569</v>
+        <v>86.27574632577509</v>
       </c>
       <c r="C18" t="n">
-        <v>35.19858948762087</v>
+        <v>41.75294802981783</v>
       </c>
       <c r="D18" t="n">
-        <v>1.238966090119051</v>
+        <v>1.533623265050873</v>
       </c>
       <c r="E18" t="n">
-        <v>11.86361189758506</v>
+        <v>12.92990018137204</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579230348240216</v>
+        <v>0.7505596721585542</v>
       </c>
       <c r="G18" t="n">
-        <v>21.36165317644845</v>
+        <v>26.57158505098427</v>
       </c>
       <c r="H18" t="n">
-        <v>37.39974410268161</v>
+        <v>37.77075314580782</v>
       </c>
       <c r="I18" t="n">
-        <v>1.585549535187372</v>
+        <v>2.028327059410567</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737018967650133</v>
+        <v>4.690997950990965</v>
       </c>
       <c r="K18" t="n">
-        <v>21.0555331955043</v>
+        <v>13.7242536742249</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69306102509241</v>
+        <v>44.45524033648707</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94718370821758</v>
+        <v>99.93244204052979</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.99062037000358</v>
+        <v>83.62548894572971</v>
       </c>
       <c r="C19" t="n">
-        <v>34.48626577610825</v>
+        <v>39.41712288110514</v>
       </c>
       <c r="D19" t="n">
-        <v>1.205263479555823</v>
+        <v>1.435541214950708</v>
       </c>
       <c r="E19" t="n">
-        <v>11.76159960579503</v>
+        <v>12.38487739989984</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583520011178615</v>
+        <v>0.7510657003852125</v>
       </c>
       <c r="G19" t="n">
-        <v>20.78056909050433</v>
+        <v>24.8722136371547</v>
       </c>
       <c r="H19" t="n">
-        <v>37.42091146253367</v>
+        <v>37.79621823265288</v>
       </c>
       <c r="I19" t="n">
-        <v>1.324224723510229</v>
+        <v>1.691412133278791</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739700006986634</v>
+        <v>4.694160627407578</v>
       </c>
       <c r="K19" t="n">
-        <v>22.00937962999642</v>
+        <v>16.3745110542703</v>
       </c>
       <c r="L19" t="n">
-        <v>43.4602387382965</v>
+        <v>44.15202364630758</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95588414440117</v>
+        <v>99.94365758168303</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.41126480915889</v>
+        <v>80.82339446574551</v>
       </c>
       <c r="C20" t="n">
-        <v>32.11034871661589</v>
+        <v>36.87652182425053</v>
       </c>
       <c r="D20" t="n">
-        <v>1.113687020517836</v>
+        <v>1.332354797696183</v>
       </c>
       <c r="E20" t="n">
-        <v>11.05195785609773</v>
+        <v>11.7297098658745</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587220897069713</v>
+        <v>0.7515025584102818</v>
       </c>
       <c r="G20" t="n">
-        <v>19.20165214298017</v>
+        <v>23.08440386361555</v>
       </c>
       <c r="H20" t="n">
-        <v>37.43917349956391</v>
+        <v>37.81820243622353</v>
       </c>
       <c r="I20" t="n">
-        <v>1.104059139623701</v>
+        <v>1.410329953861195</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74201306066857</v>
+        <v>4.696890990064261</v>
       </c>
       <c r="K20" t="n">
-        <v>24.5887351908411</v>
+        <v>19.1766055342545</v>
       </c>
       <c r="L20" t="n">
-        <v>43.2641320724455</v>
+        <v>43.89988897112611</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96321597990249</v>
+        <v>99.95301632963114</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.36284519427505</v>
+        <v>78.00556257006221</v>
       </c>
       <c r="C21" t="n">
-        <v>35.88265425644647</v>
+        <v>34.27601835017174</v>
       </c>
       <c r="D21" t="n">
-        <v>1.114369762610303</v>
+        <v>1.229107108612832</v>
       </c>
       <c r="E21" t="n">
-        <v>13.06290034001185</v>
+        <v>11.01672127989481</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591872217392064</v>
+        <v>0.7518801664955921</v>
       </c>
       <c r="G21" t="n">
-        <v>20.96819467292161</v>
+        <v>21.29553249323709</v>
       </c>
       <c r="H21" t="n">
-        <v>39.21689648080181</v>
+        <v>37.83720497833334</v>
       </c>
       <c r="I21" t="n">
-        <v>1.496376580320228</v>
+        <v>1.175865502891112</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744920135870039</v>
+        <v>4.699251040597451</v>
       </c>
       <c r="K21" t="n">
-        <v>18.63715480572496</v>
+        <v>21.99443742993778</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43034227803824</v>
+        <v>43.69036838783879</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95015134020967</v>
+        <v>99.9608241679483</v>
       </c>
     </row>
   </sheetData>
